--- a/diseases/d127/2026-2029.xlsx
+++ b/diseases/d127/2026-2029.xlsx
@@ -1708,6 +1708,151 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1741,7 +1886,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1834,7 +1979,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d127/2026-2029.xlsx
+++ b/diseases/d127/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1786,6 +1821,11 @@
       <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">

--- a/diseases/d127/2026-2029.xlsx
+++ b/diseases/d127/2026-2029.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,23 +780,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,23 +915,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,23 +1050,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,23 +1185,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,23 +1320,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,23 +1455,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,23 +1590,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>

--- a/diseases/d127/2026-2029.xlsx
+++ b/diseases/d127/2026-2029.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,13 +785,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,13 +935,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,13 +1085,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,13 +1235,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,13 +1385,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,13 +1535,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,13 +1685,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,13 +1835,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1768,6 +1888,156 @@
         </is>
       </c>
       <c r="BC9" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1806,7 +2076,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1889,7 +2159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1899,7 +2169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
